--- a/informes_data/Segunda FEB/2025-26/Regular_Season/raw/boxscore_full_analysis_2487759_LIGAREGULAROESTE.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/raw/boxscore_full_analysis_2487759_LIGAREGULAROESTE.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FullBoxScore" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,81 +614,21 @@
           <t>Gen/TO</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 37</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 40</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 49</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 50</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 51</t>
-        </is>
-      </c>
+      <c r="AL1" s="1" t="inlineStr"/>
+      <c r="AM1" s="1" t="inlineStr"/>
+      <c r="AN1" s="1" t="inlineStr"/>
+      <c r="AO1" s="1" t="inlineStr"/>
+      <c r="AP1" s="1" t="inlineStr"/>
+      <c r="AQ1" s="1" t="inlineStr"/>
+      <c r="AR1" s="1" t="inlineStr"/>
+      <c r="AS1" s="1" t="inlineStr"/>
+      <c r="AT1" s="1" t="inlineStr"/>
+      <c r="AU1" s="1" t="inlineStr"/>
+      <c r="AV1" s="1" t="inlineStr"/>
+      <c r="AW1" s="1" t="inlineStr"/>
+      <c r="AX1" s="1" t="inlineStr"/>
+      <c r="AY1" s="1" t="inlineStr"/>
+      <c r="AZ1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -740,10 +680,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -825,12 +765,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -911,13 +851,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -994,17 +934,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1219,7 +1159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>Pabellón</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1281,7 +1221,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOGROBASKET LOGI7</t>
+          <t>Lugar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1823,22 +1763,22 @@
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
         <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>5</v>
@@ -2019,16 +1959,16 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>2</v>
@@ -2215,10 +2155,10 @@
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -2227,7 +2167,7 @@
         <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
         <v>2</v>
@@ -2411,10 +2351,10 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2607,22 +2547,22 @@
         <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2999,16 +2939,16 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>4</v>
       </c>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -3783,10 +3723,10 @@
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -4159,22 +4099,22 @@
         <v>22</v>
       </c>
       <c r="R25" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="X25" t="n">
         <v>13</v>
@@ -4721,10 +4661,10 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -5113,22 +5053,22 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
+        <v>8</v>
+      </c>
+      <c r="W31" t="n">
         <v>3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>3</v>
@@ -5309,10 +5249,10 @@
         <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
         <v>2</v>
@@ -5505,10 +5445,10 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -5517,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W33" t="n">
         <v>2</v>
@@ -5701,10 +5641,10 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
@@ -5897,10 +5837,10 @@
         <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -5912,7 +5852,7 @@
         <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -6093,10 +6033,10 @@
         <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -6108,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -6289,10 +6229,10 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -6485,10 +6425,10 @@
         <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -6500,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -6861,22 +6801,22 @@
         <v>18</v>
       </c>
       <c r="R40" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="T40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U40" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X40" t="n">
         <v>14</v>
@@ -7109,7 +7049,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7171,7 +7111,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BIELE ISB</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7357,7 +7297,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CLASS BASQUET SANT ANTONI</t>
+          <t>TOunf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7667,7 +7607,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CLASS BASQUET SANT ANTONI</t>
+          <t>PLAYS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7853,7 +7793,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COTO CÓRDOBA CB</t>
+          <t>TO%</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7915,7 +7855,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7977,7 +7917,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C.B. STARLABS MORÓN</t>
+          <t>Ass/TO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8039,7 +7979,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
+          <t>Sh/TO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8163,7 +8103,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LOBE HUESCA LA MAGIA</t>
+          <t>USG%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8287,7 +8227,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMICS CASTELLÓ</t>
+          <t>pAST%</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
